--- a/config/excel/prop.xlsx
+++ b/config/excel/prop.xlsx
@@ -131,16 +131,16 @@
     <t>赵云碎片，用于合成英雄</t>
   </si>
   <si>
+    <t>招募令</t>
+  </si>
+  <si>
+    <t>招募令，用于英雄招募</t>
+  </si>
+  <si>
     <t>宠物升级丹</t>
   </si>
   <si>
     <t>宠物升级材料</t>
-  </si>
-  <si>
-    <t>招募令</t>
-  </si>
-  <si>
-    <t>招募令，用于英雄招募</t>
   </si>
   <si>
     <t>九州灵石</t>
@@ -1626,7 +1626,7 @@
         <v>35</v>
       </c>
       <c r="G13">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1646,7 +1646,7 @@
         <v>37</v>
       </c>
       <c r="G14">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="15" spans="1:7">
